--- a/report.xlsx
+++ b/report.xlsx
@@ -52,10 +52,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="_-* #\.##0.00_-;\-* #\.##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-* #\.##0\ &quot;₽&quot;_-;\-* #\.##0\ &quot;₽&quot;_-;_-* \-\ &quot;₽&quot;_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-* #\.##0_-;\-* #\.##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-* #\.##0.00\ &quot;₽&quot;_-;\-* #\.##0.00\ &quot;₽&quot;_-;_-* \-??\ &quot;₽&quot;_-;_-@_-"/>
-    <numFmt numFmtId="180" formatCode="#\ ##0.00000"/>
+    <numFmt numFmtId="177" formatCode="_-* #\.##0.00\ &quot;₽&quot;_-;\-* #\.##0.00\ &quot;₽&quot;_-;_-* \-??\ &quot;₽&quot;_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="#\ ##0.00000"/>
+    <numFmt numFmtId="179" formatCode="_-* #\.##0_-;\-* #\.##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="180" formatCode="_-* #\.##0\ &quot;₽&quot;_-;\-* #\.##0\ &quot;₽&quot;_-;_-* \-\ &quot;₽&quot;_-;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -67,7 +67,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -80,8 +80,38 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -120,6 +150,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <charset val="0"/>
@@ -143,14 +180,6 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="13"/>
       <color theme="3"/>
       <name val="Calibri"/>
@@ -158,24 +187,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FF9C6500"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -188,27 +209,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -219,55 +219,121 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -279,13 +345,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -297,109 +399,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,6 +410,54 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -439,35 +487,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -486,182 +510,158 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -721,6 +721,870 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr defTabSz="914400">
+              <a:defRPr lang="ru-RU" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t>Гистограмма времени работы </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ru-RU"/>
+              <a:t>(Task1)</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US" altLang="ru-RU"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$C$1:$G$1</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>CPU-1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>CPU-MUL</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>GPU_Float</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>GPU-Double</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>TotalTime</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$2:$G$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.922048671</c:v>
+                </c:pt>
+                <c:pt idx="3" c:formatCode="#\ ##0.00000">
+                  <c:v>1.53317</c:v>
+                </c:pt>
+                <c:pt idx="4" c:formatCode="#\ ##0.00000">
+                  <c:v>2.455218671</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="76513397"/>
+        <c:axId val="488526672"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="76513397"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="ru-RU" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="488526672"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="488526672"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="ru-RU" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="76513397"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr lang="ru-RU"/>
+      </a:pPr>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>206375</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>530225</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Диаграмма 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="2359025" y="787400"/>
+        <a:ext cx="4572000" cy="2743200"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -987,7 +1851,7 @@
     <col min="1" max="1" width="16.7142857142857" customWidth="1"/>
     <col min="2" max="2" width="15.5714285714286" customWidth="1"/>
     <col min="4" max="4" width="9.71428571428571" customWidth="1"/>
-    <col min="5" max="5" width="10.8571428571429" customWidth="1"/>
+    <col min="5" max="5" width="12.8571428571429" customWidth="1"/>
     <col min="6" max="6" width="12.7142857142857" customWidth="1"/>
     <col min="7" max="7" width="10.4285714285714" customWidth="1"/>
   </cols>
@@ -1032,14 +1896,14 @@
         <v>0.5</v>
       </c>
       <c r="E2" s="1">
-        <v>1.754603151</v>
+        <v>0.922048671</v>
       </c>
       <c r="F2" s="2">
         <v>1.53317</v>
       </c>
       <c r="G2" s="2">
         <f>E2+F2</f>
-        <v>3.287773151</v>
+        <v>2.455218671</v>
       </c>
       <c r="H2">
         <v>6</v>
@@ -1048,5 +1912,6 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>